--- a/Risks template .xlsx
+++ b/Risks template .xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/ds24853_bristol_ac_uk/Documents/Year 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meilu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D2BE44-8DE5-4E40-BE5F-0B814D2025A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45784493-771B-4D5A-95A3-AAD8A2A46C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{384F0976-F832-49BE-AD5B-6C2BA02E9446}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{384F0976-F832-49BE-AD5B-6C2BA02E9446}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Risk assesment" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +35,164 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+  <si>
+    <t>Risk ID (number)</t>
+  </si>
+  <si>
+    <t>Type of Risk</t>
+  </si>
+  <si>
+    <t>Description of Hazard</t>
+  </si>
+  <si>
+    <t>Description of Consequence or Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre- mitigation </t>
+  </si>
+  <si>
+    <t>Frequeny</t>
+  </si>
+  <si>
+    <t>Consequence</t>
+  </si>
+  <si>
+    <t>Risk number</t>
+  </si>
+  <si>
+    <t>Mitigations</t>
+  </si>
+  <si>
+    <t>Techincal</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>Electrical short circuits</t>
+  </si>
+  <si>
+    <t>Telemetry bugs and issues</t>
+  </si>
+  <si>
+    <t>Noise affecting radio link</t>
+  </si>
+  <si>
+    <t>Thermal expansion</t>
+  </si>
+  <si>
+    <t>Overheating electrical components</t>
+  </si>
+  <si>
+    <t>Scheduling</t>
+  </si>
+  <si>
+    <t>Parts order delay</t>
+  </si>
+  <si>
+    <t>Design and integration</t>
+  </si>
+  <si>
+    <t>Software development</t>
+  </si>
+  <si>
+    <t>Sensor calibration</t>
+  </si>
+  <si>
+    <t>Testing delays</t>
+  </si>
+  <si>
+    <t>Component costs</t>
+  </si>
+  <si>
+    <t>Software costs</t>
+  </si>
+  <si>
+    <t>Workshop costs</t>
+  </si>
+  <si>
+    <t>Shipping costs</t>
+  </si>
+  <si>
+    <t>Battery overheat or fire</t>
+  </si>
+  <si>
+    <t>Could damage other electrical components</t>
+  </si>
+  <si>
+    <t>Electrical components damaged - need to be reordered</t>
+  </si>
+  <si>
+    <t>May send incorrect commands to control unit</t>
+  </si>
+  <si>
+    <t>No or oncorrect commands sent to control unit</t>
+  </si>
+  <si>
+    <t>Aerodynamic shell or other componenet may be damaged</t>
+  </si>
+  <si>
+    <t>Time pressure for assembly and test</t>
+  </si>
+  <si>
+    <t>Compexity of fitting all components into RC car</t>
+  </si>
+  <si>
+    <t>May take longer than expected</t>
+  </si>
+  <si>
+    <t>Sensors may be unreliable - multiple types may need to be tested</t>
+  </si>
+  <si>
+    <t>Time pressure for record attempt</t>
+  </si>
+  <si>
+    <t>Over budget</t>
+  </si>
+  <si>
+    <t>Current sensor</t>
+  </si>
+  <si>
+    <t>Read documnetations for correct connections</t>
+  </si>
+  <si>
+    <t>Efficient and collaborative coding</t>
+  </si>
+  <si>
+    <t>Antennas to be exposed from RC car</t>
+  </si>
+  <si>
+    <t>Use materials with low expanding coefficient</t>
+  </si>
+  <si>
+    <t>Order early</t>
+  </si>
+  <si>
+    <t>Planning and coordination with other teams</t>
+  </si>
+  <si>
+    <t>Review technical documents to find sensor with best specifications</t>
+  </si>
+  <si>
+    <t>Planning and scheduling</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Sponsorships</t>
+  </si>
+  <si>
+    <t>Use of heat sink or other suitbible heat dissapation methods</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,16 +200,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -62,12 +244,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +756,465 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CE5979-8320-4A19-8AD5-A2C8FB014207}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:I19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:9" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="4"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>